--- a/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0001T0006Z000C1N54_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0001T0006Z000C1N54_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>57.6074869500034</v>
+        <v>9.361216629375553</v>
       </c>
       <c r="D2" t="n">
-        <v>57.79333759279114</v>
+        <v>9.39141735882856</v>
       </c>
       <c r="E2" t="n">
-        <v>7.91366060646323</v>
+        <v>1.285969848550275</v>
       </c>
       <c r="F2" t="n">
-        <v>7.572077539844884</v>
+        <v>1.230462600224794</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>34.25380967784342</v>
+        <v>5.566244072649556</v>
       </c>
       <c r="D3" t="n">
-        <v>35.10553882967533</v>
+        <v>5.70465005982224</v>
       </c>
       <c r="E3" t="n">
-        <v>7.91366060646323</v>
+        <v>1.285969848550275</v>
       </c>
       <c r="F3" t="n">
-        <v>7.572077539844884</v>
+        <v>1.230462600224794</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>52.08483065522366</v>
+        <v>8.463784981473845</v>
       </c>
       <c r="D4" t="n">
-        <v>51.91104670270384</v>
+        <v>8.435545089189375</v>
       </c>
       <c r="E4" t="n">
-        <v>7.91366060646323</v>
+        <v>1.285969848550275</v>
       </c>
       <c r="F4" t="n">
-        <v>7.572077539844884</v>
+        <v>1.230462600224794</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>51.04162896573167</v>
+        <v>8.294264706931397</v>
       </c>
       <c r="D5" t="n">
-        <v>49.99327175059346</v>
+        <v>8.123906659471437</v>
       </c>
       <c r="E5" t="n">
-        <v>7.91366060646323</v>
+        <v>1.285969848550275</v>
       </c>
       <c r="F5" t="n">
-        <v>7.572077539844884</v>
+        <v>1.230462600224794</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>45.55262953048357</v>
+        <v>7.402302298703581</v>
       </c>
       <c r="D6" t="n">
-        <v>45.70074495626385</v>
+        <v>7.426371055392876</v>
       </c>
       <c r="E6" t="n">
-        <v>7.91366060646323</v>
+        <v>1.285969848550275</v>
       </c>
       <c r="F6" t="n">
-        <v>7.572077539844884</v>
+        <v>1.230462600224794</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
